--- a/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,7</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 11,79</t>
+          <t>-1,68; 11,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,0</t>
+          <t>-7,12; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,8</t>
+          <t>-0,67; 5,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,28</t>
+          <t>-1,34; 4,79</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,52</t>
+          <t>-1,48; 2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,86</t>
+          <t>-1,42; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,26</t>
+          <t>-4,17; 0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,44</t>
+          <t>-4,24; 0,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,71</t>
+          <t>-2,55; 0,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,99</t>
+          <t>-2,08; 1,05</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,58; 433,08</t>
+          <t>-75,75; 374,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 402,97</t>
+          <t>-66,43; 431,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,24; 35,19</t>
+          <t>-85,21; 32,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 45,25</t>
+          <t>-84,06; 33,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,75; 50,81</t>
+          <t>-71,52; 48,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,63; 61,26</t>
+          <t>-66,1; 64,96</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,87</t>
+          <t>-3,96; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,28</t>
+          <t>-2,02; 6,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,39</t>
+          <t>-5,32; 2,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,92</t>
+          <t>-2,63; 7,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,39</t>
+          <t>-3,56; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,43</t>
+          <t>-1,02; 5,61</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 950,16</t>
+          <t>-68,78; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 279,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 552,09</t>
+          <t>-48,76; 655,5</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,79</t>
+          <t>-1,37; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,06</t>
+          <t>-0,7; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,79</t>
+          <t>-3,02; 0,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,56</t>
+          <t>-2,65; 1,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,73</t>
+          <t>-1,74; 0,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,51</t>
+          <t>-1,03; 1,64</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 313,53</t>
+          <t>-65,09; 269,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 454,94</t>
+          <t>-38,55; 417,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,29; 40,49</t>
+          <t>-78,16; 31,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,26; 83,44</t>
+          <t>-64,12; 72,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 48,28</t>
+          <t>-60,11; 54,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 94,41</t>
+          <t>-37,04; 103,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 11,16</t>
+          <t>-1,43; 13,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,0</t>
+          <t>-7,08; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,92</t>
+          <t>-0,66; 6,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,79</t>
+          <t>-1,35; 4,75</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,69</t>
+          <t>-1,47; 2,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,88</t>
+          <t>-1,21; 2,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,24</t>
+          <t>-4,69; 0,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,32</t>
+          <t>-4,32; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,78</t>
+          <t>-2,45; 0,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,05</t>
+          <t>-2,0; 1,31</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 374,38</t>
+          <t>-68,55; 613,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 431,17</t>
+          <t>-60,35; 502,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 32,7</t>
+          <t>-89,67; 30,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 33,65</t>
+          <t>-84,35; 30,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 48,92</t>
+          <t>-69,38; 46,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 64,96</t>
+          <t>-61,2; 80,42</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,86</t>
+          <t>-4,68; 1,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,52</t>
+          <t>-2,73; 6,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,31</t>
+          <t>-5,21; 2,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,64</t>
+          <t>-2,25; 8,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,33</t>
+          <t>-4,0; 1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,61</t>
+          <t>-1,13; 5,5</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,78; —</t>
+          <t>-70,53; 965,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 279,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 655,5</t>
+          <t>-43,66; 532,55</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,94</t>
+          <t>-1,17; 1,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,03</t>
+          <t>-0,45; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,47</t>
+          <t>-3,15; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,38</t>
+          <t>-2,65; 1,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,72</t>
+          <t>-1,78; 0,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,64</t>
+          <t>-1,0; 1,5</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 269,82</t>
+          <t>-60,85; 267,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 417,3</t>
+          <t>-35,38; 408,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 31,07</t>
+          <t>-75,74; 42,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 72,04</t>
+          <t>-65,43; 69,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,11; 54,03</t>
+          <t>-60,94; 48,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 103,19</t>
+          <t>-36,1; 92,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2,61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>-1,42; 11,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>-7,2; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 13,28</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,0</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,73</t>
+          <t>-0,38; 6,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 4,75</t>
+          <t>-1,33; 4,28</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>184,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>184,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,79</t>
+          <t>-4,4; 0,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,85</t>
+          <t>-3,96; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,12</t>
+          <t>-1,66; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,55</t>
+          <t>-1,33; 2,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,71</t>
+          <t>-2,36; 0,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,31</t>
+          <t>-2,27; 0,99</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-57,1%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-50,49%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>28,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>42,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-57,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-50,49%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 613,02</t>
+          <t>-89,24; 35,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 502,03</t>
+          <t>-84,06; 45,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 30,27</t>
+          <t>-72,58; 433,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 30,72</t>
+          <t>-64,02; 402,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 46,73</t>
+          <t>-67,75; 50,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 80,42</t>
+          <t>-66,63; 61,26</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,85</t>
+          <t>-5,29; 2,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,21</t>
+          <t>-2,37; 7,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,4</t>
+          <t>-4,65; 1,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,23</t>
+          <t>-2,38; 6,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,18</t>
+          <t>-3,5; 1,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,5</t>
+          <t>-0,96; 5,43</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-37,84%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-49,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>92,23%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-37,84%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1024,19 +1024,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-74,07; 950,16</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-70,53; 965,42</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,66; 532,55</t>
+          <t>-47,58; 552,09</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,15</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,85</t>
+          <t>-3,14; 0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,9</t>
+          <t>-2,63; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 0,66</t>
+          <t>-1,17; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,35</t>
+          <t>-0,49; 3,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,73</t>
+          <t>-1,69; 0,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,5</t>
+          <t>-1,08; 1,51</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-40,5%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,11%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>16,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>82,66%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-40,5%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 267,64</t>
+          <t>-76,29; 40,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 408,48</t>
+          <t>-66,26; 83,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 42,4</t>
+          <t>-62,92; 313,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 69,45</t>
+          <t>-37,11; 454,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 48,64</t>
+          <t>-60,39; 48,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 92,91</t>
+          <t>-37,48; 94,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,299 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.597661283849459</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.406425072020193</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.30691246819174</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.612627370636365</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.929271377878779</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.5111770387687574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,42; 11,79</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,7</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 6,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 4,28</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.422908233583308</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.198307205962176</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.3757503495976067</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.334877422625526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>184,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>287,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.79271290221585</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.091346235724813</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.69688009763606</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.797257073653872</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.284448164364981</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1.846995858882244</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.872564948527589</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.7611107804199868</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 0,26</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 0,44</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 2,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 2,86</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 0,71</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 0,99</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-57,1%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-50,49%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-32,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-23,23%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-1.99486392594974</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.76375452093692</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.435727106645652</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6558893411347556</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.8247640907102018</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.5915865015504982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-89,24; 35,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-84,06; 45,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-72,58; 433,08</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-64,02; 402,97</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-67,75; 50,81</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-66,63; 61,26</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.399355299387602</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.960045206757702</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.663461141372437</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.331957946658009</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.360590435375659</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-2.269640522597877</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2589014619792055</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4402382175000931</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.522670359631257</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.860333697344898</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.7080316573726484</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.994706357623386</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 2,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 7,92</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 1,87</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 6,28</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 1,39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,96; 5,43</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.5710056160407772</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.5048533504824455</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.2850407274985424</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.4290648254473382</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3237938982671295</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2322507752905489</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-37,84%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-49,85%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-42,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.8923883849861394</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.840552448954576</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.725796841576409</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6401911401167912</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6775249015592152</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6662602290022276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-74,07; 950,16</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-47,58; 552,09</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.3518700522311918</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.4525066370484359</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>4.330790279939486</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>4.02968762221274</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5081380471080422</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6125661035667745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +900,301 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.9842489966549187</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.516766656344351</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.9238702577233618</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.709342743691051</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.9478360981369635</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.124950709227441</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,14; 0,79</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 1,56</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,17; 1,79</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 3,06</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 0,73</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-1,08; 1,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.289168816804116</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.370048112661578</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.649342255997156</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.384390220464452</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.500520792078606</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.9598927220823135</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-40,5%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-21,11%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-22,9%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.394173317625059</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.916762992337153</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.868156683422543</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.282915465185981</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.388435784491312</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.425995635897682</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-76,29; 40,49</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-66,26; 83,44</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-62,92; 313,53</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-37,11; 454,94</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-60,39; 48,28</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-37,48; 94,41</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-0.3784229822012079</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.9676437027980103</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.4984901619594336</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.9223054146655725</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4268214395705927</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.9568896167931656</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="n">
+        <v>-0.7407314475042017</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-0.4758474216373978</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="n">
+        <v>9.501632950359507</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>5.52094008739205</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.241488383824592</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.6472088190331502</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.2360616390854485</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.152519072013522</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.5134548852095226</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.2391598024612064</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.1428796236888</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.629247092889194</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.169657993866316</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4876473702858471</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1.68716827095266</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.078405695225659</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.7895178502104198</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.559256516606088</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.786712949719856</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.057297330419533</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.7250432878563002</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.51072141168088</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.4049630445802636</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2111140605499958</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1693092040139873</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.8266149783994159</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2289511808045174</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.1066421232940931</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.7629099489323322</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.662601089119085</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.6292198848400825</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3710997030227237</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6038524801942992</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3748402237780855</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.4048650714315569</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.8344308912563757</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>3.135301938336491</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>4.549357587259101</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.4827830745893852</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.9441438618958976</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1202,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
